--- a/artfynd/A 17061-2020 artfynd.xlsx
+++ b/artfynd/A 17061-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 17061-2020 artfynd.xlsx
+++ b/artfynd/A 17061-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2090,10 +2090,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>84049890</v>
+        <v>84049699</v>
       </c>
       <c r="B14" t="n">
-        <v>95511</v>
+        <v>98520</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2106,21 +2106,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221944</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539114.970940541</v>
+        <v>539080.8169862654</v>
       </c>
       <c r="R14" t="n">
-        <v>6350967.853599045</v>
+        <v>6350916.201116317</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2207,7 +2207,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>84049699</v>
+        <v>84050161</v>
       </c>
       <c r="B15" t="n">
         <v>98520</v>
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>539080.8169862654</v>
+        <v>538831.8600352291</v>
       </c>
       <c r="R15" t="n">
-        <v>6350916.201116317</v>
+        <v>6350852.243983855</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>84050161</v>
+        <v>84050080</v>
       </c>
       <c r="B16" t="n">
-        <v>98520</v>
+        <v>103265</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2340,21 +2340,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>538831.8600352291</v>
+        <v>538969.8220925292</v>
       </c>
       <c r="R16" t="n">
-        <v>6350852.243983855</v>
+        <v>6350861.116223728</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>84050080</v>
+        <v>99409817</v>
       </c>
       <c r="B17" t="n">
-        <v>103265</v>
+        <v>96334</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2453,28 +2453,32 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
@@ -2485,13 +2489,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>538969.8220925292</v>
+        <v>539040.9185556143</v>
       </c>
       <c r="R17" t="n">
-        <v>6350861.116223728</v>
+        <v>6350842.341502216</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2515,7 +2519,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2020-04-01</t>
+          <t>2022-03-23</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -2525,7 +2529,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2020-04-01</t>
+          <t>2022-03-23</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -2558,10 +2562,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>99409817</v>
+        <v>99410157</v>
       </c>
       <c r="B18" t="n">
-        <v>96334</v>
+        <v>98520</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2570,32 +2574,28 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>539040.9185556143</v>
+        <v>539090.5638972528</v>
       </c>
       <c r="R18" t="n">
-        <v>6350842.341502216</v>
+        <v>6350802.291731087</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2679,7 +2679,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>99410157</v>
+        <v>99409788</v>
       </c>
       <c r="B19" t="n">
         <v>98520</v>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>539090.5638972528</v>
+        <v>539065.4678761252</v>
       </c>
       <c r="R19" t="n">
-        <v>6350802.291731087</v>
+        <v>6350822.584140129</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2793,123 +2793,6 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>99409788</v>
-      </c>
-      <c r="B20" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Västrahult, Sm</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>539065.4678761252</v>
-      </c>
-      <c r="R20" t="n">
-        <v>6350822.584140129</v>
-      </c>
-      <c r="S20" t="n">
-        <v>5</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Hultsfred</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Virserum</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2022-03-23</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2022-03-23</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="inlineStr"/>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
